--- a/P4/qnap/out-h.xlsx
+++ b/P4/qnap/out-h.xlsx
@@ -8,23 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hexdhog/Documents/uib/CS/Y2/ACSI/P4/qnap/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C65A7F9C-8DF1-CF4E-AC50-F6FF30939CFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C02942A-70C1-3F4C-9DF2-E5ECA12B71C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3160" yWindow="2980" windowWidth="28040" windowHeight="17440" xr2:uid="{F32EDD6A-8D96-964B-95F0-0A2D42905EF5}"/>
+    <workbookView xWindow="2540" yWindow="4820" windowWidth="30160" windowHeight="15520" xr2:uid="{F32EDD6A-8D96-964B-95F0-0A2D42905EF5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">Sheet1!$A$2:$A$11</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">Sheet1!$B$2:$B$11</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">Sheet1!$B$2:$B$11</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">Sheet1!$A$1</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">Sheet1!$A$2:$A$11</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">Sheet1!$B$1</definedName>
-    <definedName name="_xlchart.v1.6" hidden="1">Sheet1!$B$2:$B$11</definedName>
-    <definedName name="_xlchart.v1.7" hidden="1">Sheet1!$B$2:$B$11</definedName>
-  </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -219,34 +209,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>0.45689999999999997</c:v>
+                  <c:v>0.63900000000000001</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.77869999999999995</c:v>
+                  <c:v>0.99229999999999996</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.1667000000000001</c:v>
+                  <c:v>1.917</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3.8050000000000002</c:v>
+                  <c:v>4.0750000000000002</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>6.7290000000000001</c:v>
+                  <c:v>7.0010000000000003</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>9.7279999999999998</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>12.73</c:v>
+                  <c:v>13</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>15.73</c:v>
+                  <c:v>16</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>18.73</c:v>
+                  <c:v>19</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>21.73</c:v>
+                  <c:v>22</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1019,15 +1009,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>742950</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>69850</xdr:rowOff>
+      <xdr:colOff>603250</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>342900</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>63500</xdr:rowOff>
+      <xdr:colOff>203200</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>50800</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -1388,7 +1378,7 @@
         <v>10</v>
       </c>
       <c r="B2">
-        <v>0.45689999999999997</v>
+        <v>0.63900000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -1396,7 +1386,7 @@
         <v>20</v>
       </c>
       <c r="B3">
-        <v>0.77869999999999995</v>
+        <v>0.99229999999999996</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
@@ -1404,7 +1394,7 @@
         <v>30</v>
       </c>
       <c r="B4">
-        <v>1.1667000000000001</v>
+        <v>1.917</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -1412,7 +1402,7 @@
         <v>40</v>
       </c>
       <c r="B5">
-        <v>3.8050000000000002</v>
+        <v>4.0750000000000002</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
@@ -1420,7 +1410,7 @@
         <v>50</v>
       </c>
       <c r="B6">
-        <v>6.7290000000000001</v>
+        <v>7.0010000000000003</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
@@ -1428,7 +1418,7 @@
         <v>60</v>
       </c>
       <c r="B7">
-        <v>9.7279999999999998</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
@@ -1436,7 +1426,7 @@
         <v>70</v>
       </c>
       <c r="B8">
-        <v>12.73</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
@@ -1444,7 +1434,7 @@
         <v>80</v>
       </c>
       <c r="B9">
-        <v>15.73</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
@@ -1452,7 +1442,7 @@
         <v>90</v>
       </c>
       <c r="B10">
-        <v>18.73</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
@@ -1460,7 +1450,7 @@
         <v>100</v>
       </c>
       <c r="B11">
-        <v>21.73</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
